--- a/artfynd/A 33558-2026 artfynd.xlsx
+++ b/artfynd/A 33558-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136191733</v>
       </c>
       <c r="B2" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136191734</v>
       </c>
       <c r="B4" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136596825</v>
       </c>
       <c r="B5" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33558-2026 artfynd.xlsx
+++ b/artfynd/A 33558-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136191733</v>
       </c>
       <c r="B2" t="n">
-        <v>92162</v>
+        <v>92163</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136191734</v>
       </c>
       <c r="B4" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136596825</v>
       </c>
       <c r="B5" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33558-2026 artfynd.xlsx
+++ b/artfynd/A 33558-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136191733</v>
       </c>
       <c r="B2" t="n">
-        <v>92163</v>
+        <v>92168</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>136191735</v>
       </c>
       <c r="B3" t="n">
-        <v>58843</v>
+        <v>58845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136191734</v>
       </c>
       <c r="B4" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>136596825</v>
       </c>
       <c r="B5" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33558-2026 artfynd.xlsx
+++ b/artfynd/A 33558-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136191733</v>
+        <v>136819449</v>
       </c>
       <c r="B2" t="n">
-        <v>92168</v>
+        <v>92095</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5321</v>
+        <v>4660</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ranebo, Boh</t>
+          <t>Ranebo-Bolsjön vattenskyddsområdet, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>294004</v>
+        <v>293983</v>
       </c>
       <c r="R2" t="n">
-        <v>6522710</v>
+        <v>6522396</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,45 +766,30 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136191733</t>
+          <t>https://artportalen.se/Sighting/136819449</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136191735</v>
+        <v>136191733</v>
       </c>
       <c r="B3" t="n">
-        <v>58845</v>
+        <v>92168</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>5321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>293963</v>
+        <v>294004</v>
       </c>
       <c r="R3" t="n">
-        <v>6522686</v>
+        <v>6522710</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -877,8 +865,24 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -894,54 +898,57 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136191735</t>
+          <t>https://artportalen.se/Sighting/136191733</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136191734</v>
+        <v>136819214</v>
       </c>
       <c r="B4" t="n">
-        <v>98213</v>
+        <v>75566</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ranebo, Boh</t>
+          <t>Ranebo-Bolsjön vattenskyddsområdet, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>293961</v>
+        <v>294000</v>
       </c>
       <c r="R4" t="n">
-        <v>6522700</v>
+        <v>6522601</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,12 +972,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,75 +986,75 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136191734</t>
+          <t>https://artportalen.se/Sighting/136819214</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136596825</v>
+        <v>136819374</v>
       </c>
       <c r="B5" t="n">
-        <v>98213</v>
+        <v>75566</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6426</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ranebo, Ranebo, Boh</t>
+          <t>Ranebo-Bolsjön vattenskyddsområdet, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>294073</v>
+        <v>293999</v>
       </c>
       <c r="R5" t="n">
-        <v>6522584</v>
+        <v>6522515</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,22 +1078,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:03</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:03</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,24 +1092,1235 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna  Hansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna  Hansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136819374</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136819201</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ranebo-Bolsjön vattenskyddsområdet, Boh</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>293966</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6522607</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Den sågs- och hördes mycket i den gamla kontinuitetsskogen som markägaren tänker kalavverka.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136819201</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136819297</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ranebo-Bolsjön vattenskyddsområdet, Boh</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>293976</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6522533</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136819297</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136819359</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ranebo-Bolsjön vattenskyddsområdet, Boh</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>293987</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6522526</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136819359</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136819433</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ranebo-Bolsjön vattenskyddsområdet, Boh</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>294011</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6522456</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136819433</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136819475</v>
+      </c>
+      <c r="B10" t="n">
+        <v>4777</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ranebo-Bolsjön vattenskyddsområdet, Boh</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>293962</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6522394</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136819475</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136819840</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56875</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ranebo-Bolsjön vattenskyddsområdet, Boh</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>294063</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6522660</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136819840</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136191735</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58845</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ranebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>293963</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6522686</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136191735</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136191734</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98213</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ranebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>293961</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6522700</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136191734</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136596825</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98213</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ranebo, Ranebo, Boh</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>294073</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6522584</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anna  Hansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anna  Hansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136596825</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136819144</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98213</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ranebo-Bolsjön vattenskyddsområdet, Boh</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>293967</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6522574</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136819144</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136819336</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98213</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ranebo-Bolsjön vattenskyddsområdet, Boh</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>294002</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6522530</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lur</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136819336</t>
         </is>
       </c>
     </row>
@@ -1122,6 +2330,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33558-2026 artfynd.xlsx
+++ b/artfynd/A 33558-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136819449</v>
       </c>
       <c r="B2" t="n">
-        <v>92095</v>
+        <v>92097</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136191733</v>
       </c>
       <c r="B3" t="n">
-        <v>92168</v>
+        <v>92170</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>136191734</v>
       </c>
       <c r="B13" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136596825</v>
       </c>
       <c r="B14" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136819144</v>
       </c>
       <c r="B15" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>136819336</v>
       </c>
       <c r="B16" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 33558-2026 artfynd.xlsx
+++ b/artfynd/A 33558-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136819449</v>
       </c>
       <c r="B2" t="n">
-        <v>92097</v>
+        <v>92099</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136596825</v>
       </c>
       <c r="B14" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136819144</v>
       </c>
       <c r="B15" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>136819336</v>
       </c>
       <c r="B16" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 33558-2026 artfynd.xlsx
+++ b/artfynd/A 33558-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136819449</v>
       </c>
       <c r="B2" t="n">
-        <v>92099</v>
+        <v>92101</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136596825</v>
       </c>
       <c r="B14" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136819144</v>
       </c>
       <c r="B15" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>136819336</v>
       </c>
       <c r="B16" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 33558-2026 artfynd.xlsx
+++ b/artfynd/A 33558-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136819449</v>
       </c>
       <c r="B2" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136596825</v>
       </c>
       <c r="B14" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136819144</v>
       </c>
       <c r="B15" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>136819336</v>
       </c>
       <c r="B16" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 33558-2026 artfynd.xlsx
+++ b/artfynd/A 33558-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136819449</v>
       </c>
       <c r="B2" t="n">
-        <v>92102</v>
+        <v>92108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136596825</v>
       </c>
       <c r="B14" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136819144</v>
       </c>
       <c r="B15" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>136819336</v>
       </c>
       <c r="B16" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 33558-2026 artfynd.xlsx
+++ b/artfynd/A 33558-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136819449</v>
       </c>
       <c r="B2" t="n">
-        <v>92108</v>
+        <v>92112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136596825</v>
       </c>
       <c r="B14" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136819144</v>
       </c>
       <c r="B15" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>136819336</v>
       </c>
       <c r="B16" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 33558-2026 artfynd.xlsx
+++ b/artfynd/A 33558-2026 artfynd.xlsx
@@ -1999,7 +1999,7 @@
         <v>136596825</v>
       </c>
       <c r="B14" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136819144</v>
       </c>
       <c r="B15" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>136819336</v>
       </c>
       <c r="B16" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 33558-2026 artfynd.xlsx
+++ b/artfynd/A 33558-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136819449</v>
       </c>
       <c r="B2" t="n">
-        <v>92112</v>
+        <v>92114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136596825</v>
       </c>
       <c r="B14" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136819144</v>
       </c>
       <c r="B15" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>136819336</v>
       </c>
       <c r="B16" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 33558-2026 artfynd.xlsx
+++ b/artfynd/A 33558-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136819449</v>
       </c>
       <c r="B2" t="n">
-        <v>92114</v>
+        <v>92127</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136819214</v>
       </c>
       <c r="B4" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136819374</v>
       </c>
       <c r="B5" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>136819201</v>
       </c>
       <c r="B6" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>136819297</v>
       </c>
       <c r="B7" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136819359</v>
       </c>
       <c r="B8" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>136819433</v>
       </c>
       <c r="B9" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>136819840</v>
       </c>
       <c r="B11" t="n">
-        <v>56875</v>
+        <v>56888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>136596825</v>
       </c>
       <c r="B14" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136819144</v>
       </c>
       <c r="B15" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>136819336</v>
       </c>
       <c r="B16" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 33558-2026 artfynd.xlsx
+++ b/artfynd/A 33558-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136819449</v>
       </c>
       <c r="B2" t="n">
-        <v>92127</v>
+        <v>92129</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136819214</v>
       </c>
       <c r="B4" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136819374</v>
       </c>
       <c r="B5" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>136819201</v>
       </c>
       <c r="B6" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>136819297</v>
       </c>
       <c r="B7" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>136819359</v>
       </c>
       <c r="B8" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>136819433</v>
       </c>
       <c r="B9" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>136819840</v>
       </c>
       <c r="B11" t="n">
-        <v>56888</v>
+        <v>56890</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136819144</v>
       </c>
       <c r="B15" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>136819336</v>
       </c>
       <c r="B16" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 33558-2026 artfynd.xlsx
+++ b/artfynd/A 33558-2026 artfynd.xlsx
@@ -1149,21 +1149,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1274,11 +1262,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1384,11 +1368,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1494,11 +1474,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>

--- a/artfynd/A 33558-2026 artfynd.xlsx
+++ b/artfynd/A 33558-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136819449</v>
       </c>
       <c r="B2" t="n">
-        <v>92129</v>
+        <v>92132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>136819144</v>
       </c>
       <c r="B15" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>136819336</v>
       </c>
       <c r="B16" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 33558-2026 artfynd.xlsx
+++ b/artfynd/A 33558-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136819449</v>
       </c>
       <c r="B2" t="n">
-        <v>92132</v>
+        <v>92142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136819214</v>
       </c>
       <c r="B4" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136819374</v>
       </c>
       <c r="B5" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>136819201</v>
       </c>
       <c r="B6" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>136819297</v>
       </c>
       <c r="B7" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136819359</v>
       </c>
       <c r="B8" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>136819433</v>
       </c>
       <c r="B9" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>136819475</v>
       </c>
       <c r="B10" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>136819840</v>
       </c>
       <c r="B11" t="n">
-        <v>56890</v>
+        <v>56900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>136819144</v>
       </c>
       <c r="B15" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>136819336</v>
       </c>
       <c r="B16" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 33558-2026 artfynd.xlsx
+++ b/artfynd/A 33558-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136819449</v>
       </c>
       <c r="B2" t="n">
-        <v>92142</v>
+        <v>92143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>136819144</v>
       </c>
       <c r="B15" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>136819336</v>
       </c>
       <c r="B16" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 33558-2026 artfynd.xlsx
+++ b/artfynd/A 33558-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136819449</v>
       </c>
       <c r="B2" t="n">
-        <v>92143</v>
+        <v>92146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136819214</v>
       </c>
       <c r="B4" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136819374</v>
       </c>
       <c r="B5" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>136819201</v>
       </c>
       <c r="B6" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>136819297</v>
       </c>
       <c r="B7" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136819359</v>
       </c>
       <c r="B8" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>136819433</v>
       </c>
       <c r="B9" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>136819840</v>
       </c>
       <c r="B11" t="n">
-        <v>56900</v>
+        <v>56901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>136819144</v>
       </c>
       <c r="B15" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>136819336</v>
       </c>
       <c r="B16" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 33558-2026 artfynd.xlsx
+++ b/artfynd/A 33558-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136819449</v>
       </c>
       <c r="B2" t="n">
-        <v>92146</v>
+        <v>92148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>136819144</v>
       </c>
       <c r="B15" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>136819336</v>
       </c>
       <c r="B16" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 33558-2026 artfynd.xlsx
+++ b/artfynd/A 33558-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136819449</v>
       </c>
       <c r="B2" t="n">
-        <v>92148</v>
+        <v>92153</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136819214</v>
       </c>
       <c r="B4" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136819374</v>
       </c>
       <c r="B5" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>136819201</v>
       </c>
       <c r="B6" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>136819297</v>
       </c>
       <c r="B7" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>136819359</v>
       </c>
       <c r="B8" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>136819433</v>
       </c>
       <c r="B9" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>136819144</v>
       </c>
       <c r="B15" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>136819336</v>
       </c>
       <c r="B16" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
